--- a/src/grafs_e/data/scenario_region/Exponential/Savoie.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Savoie.xlsx
@@ -438,6 +438,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -459,6 +460,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -487,6 +489,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -494,6 +497,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -501,6 +505,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -533,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -764,23 +769,6 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Methanisation</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>GWh</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2021 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1664,7 +1652,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1720,37 +1708,41 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Weight export</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
+          <t>N recycling rate of human excretion in urban area</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Weight for the optimization model</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Weight energy</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
+          <t>N recycling rate of human excretion in rural area</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Weight for the optimization model</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1767,7 +1759,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1784,41 +1776,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1835,7 +1827,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1852,7 +1844,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1869,7 +1861,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1886,41 +1878,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1937,7 +1929,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1954,7 +1946,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1971,7 +1963,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1988,7 +1980,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2005,7 +1997,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2022,7 +2014,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2039,7 +2031,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2056,7 +2048,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2073,7 +2065,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2090,7 +2082,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2107,7 +2099,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2124,7 +2116,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2141,7 +2133,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2158,7 +2150,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2175,7 +2167,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2192,7 +2184,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2209,7 +2201,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2226,7 +2218,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2243,7 +2235,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2260,7 +2252,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2277,7 +2269,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2294,12 +2286,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2311,12 +2303,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2328,7 +2320,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2345,7 +2337,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2362,7 +2354,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2379,7 +2371,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2396,41 +2388,41 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2447,7 +2439,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2464,7 +2456,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2481,7 +2473,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2498,12 +2490,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>kg/LU</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2515,12 +2507,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>kg/LU</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2532,7 +2524,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Caprines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2549,7 +2541,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Poultry dairy productivity</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2558,40 +2550,6 @@
         </is>
       </c>
       <c r="E55" t="inlineStr">
-        <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Caprines dairy productivity</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Poultry dairy productivity</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>

--- a/src/grafs_e/data/scenario_region/Exponential/Savoie.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Savoie.xlsx
@@ -438,9 +438,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -462,9 +460,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -493,9 +489,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -503,9 +497,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -513,9 +505,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -548,31 +538,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Business as usual</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
@@ -589,8 +579,6 @@
           <t>M inhabitant</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>INSEE data</t>
@@ -608,8 +596,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Logistic</t>
@@ -627,8 +613,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -646,8 +630,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -665,8 +647,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -684,8 +664,6 @@
           <t>ha</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -703,8 +681,6 @@
           <t>ha</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -714,7 +690,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Net import of vegetal pdcts</t>
+          <t>Import of vegetal pdcts</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -722,66 +698,75 @@
           <t>ktN</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Historical trend. Used as a goal but may be adjusted according to territory situation</t>
+          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Total LU</t>
+          <t>Export of vegetal pdcts</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>ktN</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend, see prop for each livestock in technical sheet</t>
+          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Synth N fertilizer application to cropland</t>
+          <t>Total LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN/ha/yr</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>LU</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>No business as usual: computed with optimization model to fertilize all crops</t>
+          <t>Historical trend, see prop for each livestock in technical sheet</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Synth N fertilizer application to cropland</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>kgN/ha/yr</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Synth N fertilizer application to grassland</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>kgN/ha/yr</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
         </is>
@@ -1181,7 +1166,6 @@
       <c r="E17" t="n">
         <v>43</v>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1607,7 +1591,6 @@
           <t xml:space="preserve">Natural meadow </t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="b">
         <v>0</v>
       </c>
@@ -1632,31 +1615,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Business as usual</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
@@ -1668,11 +1651,9 @@
           <t>Weight diet</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1685,11 +1666,9 @@
           <t>Weight synthetic fertilizer use</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>5</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1699,14 +1678,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Weight import/export balance</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>Weight import</t>
+        </is>
+      </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1716,26 +1693,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>Weight export</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1743,8 +1716,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1754,7 +1725,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1762,8 +1733,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1773,7 +1742,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1781,8 +1750,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1792,26 +1759,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kgN</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1819,8 +1784,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1830,7 +1793,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1838,8 +1801,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1849,7 +1810,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1857,8 +1818,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1868,7 +1827,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1876,8 +1835,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1887,7 +1844,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1895,8 +1852,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1906,26 +1861,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>kgN</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1933,8 +1886,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1944,7 +1895,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1952,8 +1903,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1963,7 +1912,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1971,8 +1920,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1982,7 +1929,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1990,8 +1937,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2001,7 +1946,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2009,8 +1954,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2020,7 +1963,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2028,8 +1971,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2039,7 +1980,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2047,8 +1988,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2058,7 +1997,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2066,8 +2005,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2077,7 +2014,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2085,8 +2022,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2096,7 +2031,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2104,8 +2039,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2115,7 +2048,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2123,8 +2056,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2134,7 +2065,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2142,8 +2073,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2153,7 +2082,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2161,8 +2090,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2172,7 +2099,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2180,8 +2107,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2191,7 +2116,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2199,8 +2124,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2210,7 +2133,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2218,8 +2141,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2229,7 +2150,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2237,8 +2158,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2248,7 +2167,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2256,8 +2175,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2267,7 +2184,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2275,8 +2192,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2286,7 +2201,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2294,8 +2209,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2305,7 +2218,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2313,8 +2226,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2324,7 +2235,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2332,8 +2243,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2343,7 +2252,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2351,8 +2260,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2362,16 +2269,14 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2381,7 +2286,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2389,8 +2294,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2400,7 +2303,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2408,8 +2311,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2419,7 +2320,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2427,8 +2328,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2438,7 +2337,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2446,8 +2345,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2457,7 +2354,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2465,8 +2362,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2476,26 +2371,24 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+          <t>prop</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2503,8 +2396,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2514,7 +2405,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2522,8 +2413,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2533,7 +2422,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2541,8 +2430,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2552,7 +2439,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2560,8 +2447,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2571,7 +2456,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2579,8 +2464,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2590,16 +2473,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+          <t>kgcarcass/LU</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2609,7 +2490,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2617,8 +2498,6 @@
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2628,7 +2507,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2636,8 +2515,6 @@
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2647,17 +2524,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>

--- a/src/grafs_e/data/scenario_region/Exponential/Savoie.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Savoie.xlsx
@@ -438,7 +438,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -460,7 +459,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -489,7 +487,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -497,7 +494,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -505,7 +501,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -538,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,6 +764,23 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Methanisation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2021 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1652,7 +1664,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1708,41 +1720,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight export</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight energy</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1759,7 +1767,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1776,41 +1784,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1827,7 +1835,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1844,7 +1852,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1861,7 +1869,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1878,41 +1886,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1929,7 +1937,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1946,7 +1954,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1963,7 +1971,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1980,7 +1988,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1997,7 +2005,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2014,7 +2022,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2031,7 +2039,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2048,7 +2056,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2065,7 +2073,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2082,7 +2090,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2099,7 +2107,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2116,7 +2124,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2133,7 +2141,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2150,7 +2158,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2167,7 +2175,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2184,7 +2192,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2201,7 +2209,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2218,7 +2226,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2235,7 +2243,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2252,7 +2260,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2269,7 +2277,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2286,12 +2294,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2303,12 +2311,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2320,7 +2328,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2337,7 +2345,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2354,7 +2362,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2371,7 +2379,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2388,41 +2396,41 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2439,7 +2447,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2456,7 +2464,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2473,7 +2481,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2490,12 +2498,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2507,12 +2515,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2524,7 +2532,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2541,15 +2549,49 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Ovines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>

--- a/src/grafs_e/data/scenario_region/Exponential/Savoie.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Savoie.xlsx
@@ -438,7 +438,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -460,7 +459,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -489,7 +487,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -497,7 +494,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -505,7 +501,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -538,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,6 +764,23 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Methaniser production</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GWh/yr</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Regional 2021 data mapped on 2006 33 region plant production. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1652,7 +1664,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1708,24 +1720,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight energy</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1742,7 +1752,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1759,7 +1769,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1776,24 +1786,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1810,7 +1820,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1827,7 +1837,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1844,7 +1854,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1861,7 +1871,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1878,24 +1888,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1912,7 +1922,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1929,7 +1939,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1946,7 +1956,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1963,7 +1973,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1980,7 +1990,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1997,7 +2007,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2014,7 +2024,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2031,7 +2041,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2048,7 +2058,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2065,7 +2075,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2082,7 +2092,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2099,7 +2109,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2116,7 +2126,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2133,7 +2143,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2150,7 +2160,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2167,7 +2177,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2184,7 +2194,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2201,7 +2211,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2218,7 +2228,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2235,7 +2245,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2252,7 +2262,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2269,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2286,12 +2296,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2303,7 +2313,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2320,7 +2330,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2337,7 +2347,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2354,7 +2364,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2371,7 +2381,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2388,24 +2398,24 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2422,7 +2432,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2439,7 +2449,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2456,7 +2466,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2473,7 +2483,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2490,12 +2500,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2507,7 +2517,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2524,7 +2534,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2541,15 +2551,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>

--- a/src/grafs_e/data/scenario_region/Exponential/Savoie.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Savoie.xlsx
@@ -1627,7 +1627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1735,24 +1735,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight methaniser input</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>25</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1769,7 +1767,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1786,7 +1784,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1803,24 +1801,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1837,7 +1835,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1854,7 +1852,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1871,7 +1869,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1888,7 +1886,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1905,24 +1903,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1939,7 +1937,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1956,7 +1954,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1973,7 +1971,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1990,7 +1988,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2007,7 +2005,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2024,7 +2022,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2041,7 +2039,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2058,7 +2056,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2075,7 +2073,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2092,7 +2090,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2109,7 +2107,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2126,7 +2124,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2143,7 +2141,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2160,7 +2158,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2177,7 +2175,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2194,7 +2192,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2211,7 +2209,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2228,7 +2226,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2245,7 +2243,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2262,7 +2260,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2277,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2296,7 +2294,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2313,12 +2311,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2330,7 +2328,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2347,7 +2345,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2364,7 +2362,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2381,7 +2379,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2398,7 +2396,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2415,24 +2413,24 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2449,7 +2447,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2466,7 +2464,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2483,7 +2481,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2500,7 +2498,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2517,12 +2515,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2534,7 +2532,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2551,7 +2549,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2568,17 +2566,134 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Share of crop residues in methaniser</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Share of green waste in methaniser</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Share of dedicated culture in methaniser</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Share of animal food industry in methaniser</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Share of livestock effluent in methaniser</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
         </is>
       </c>
     </row>

--- a/src/grafs_e/data/scenario_region/Exponential/Savoie.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Savoie.xlsx
@@ -438,9 +438,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -462,9 +459,6 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -493,9 +487,6 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -503,18 +494,12 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
           <t>BAU compute Business as usual scenario</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -548,31 +533,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Business as usual</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
@@ -589,8 +574,6 @@
           <t>M inhabitant</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>INSEE data</t>
@@ -608,8 +591,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Logistic</t>
@@ -627,8 +608,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -646,8 +625,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -665,8 +642,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -684,8 +659,6 @@
           <t>ha</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -703,8 +676,6 @@
           <t>ha</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -714,7 +685,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Net import of vegetal pdcts</t>
+          <t>Import of vegetal pdcts</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -722,68 +693,94 @@
           <t>ktN</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Historical trend. Used as a goal but may be adjusted according to territory situation</t>
+          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Total LU</t>
+          <t>Export of vegetal pdcts</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>ktN</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend, see prop for each livestock in technical sheet</t>
+          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Synth N fertilizer application to cropland</t>
+          <t>Total LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN/ha/yr</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>LU</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>No business as usual: computed with optimization model to fertilize all crops</t>
+          <t>Historical trend, see prop for each livestock in technical sheet</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Synth N fertilizer application to cropland</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>kgN/ha/yr</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Synth N fertilizer application to grassland</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>kgN/ha/yr</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Methaniser production</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GWh/yr</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Regional 2021 data mapped on 2006 33 region plant production. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1178,6 @@
       <c r="E17" t="n">
         <v>43</v>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1607,7 +1603,6 @@
           <t xml:space="preserve">Natural meadow </t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="b">
         <v>0</v>
       </c>
@@ -1632,31 +1627,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Business as usual</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
@@ -1668,11 +1663,9 @@
           <t>Weight diet</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>10</v>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1685,11 +1678,9 @@
           <t>Weight synthetic fertilizer use</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>5</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1699,14 +1690,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Weight import/export balance</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>Weight import</t>
+        </is>
+      </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1716,64 +1705,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>Weight export</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+          <t>Weight energy</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+          <t>Weight methaniser input</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>25</v>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1781,8 +1758,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1792,64 +1767,58 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kgN</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kgN</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1857,8 +1826,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1868,7 +1835,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1876,8 +1843,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1887,7 +1852,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1895,8 +1860,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1906,64 +1869,58 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>kgN</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>kgN</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t>kgN</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1971,8 +1928,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1982,7 +1937,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1990,8 +1945,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2001,7 +1954,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2009,8 +1962,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2020,7 +1971,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2028,8 +1979,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2039,7 +1988,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2047,8 +1996,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2058,7 +2005,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2066,8 +2013,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2077,7 +2022,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2085,8 +2030,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2096,7 +2039,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2104,8 +2047,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2115,7 +2056,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2123,8 +2064,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2134,7 +2073,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2142,8 +2081,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2153,7 +2090,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2161,8 +2098,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2172,7 +2107,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2180,8 +2115,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2191,7 +2124,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2199,8 +2132,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2210,7 +2141,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2218,8 +2149,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2229,7 +2158,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2237,8 +2166,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2248,7 +2175,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2256,8 +2183,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2267,7 +2192,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2275,8 +2200,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2286,7 +2209,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2294,8 +2217,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2305,7 +2226,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2313,8 +2234,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2324,7 +2243,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2332,8 +2251,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2343,7 +2260,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2351,8 +2268,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2362,16 +2277,14 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2381,16 +2294,14 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2400,16 +2311,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2419,7 +2328,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2427,8 +2336,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2438,7 +2345,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2446,8 +2353,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2457,7 +2362,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2465,8 +2370,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2476,64 +2379,58 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+          <t>prop</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+          <t>prop</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+          <t>prop</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2541,8 +2438,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2552,7 +2447,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2560,8 +2455,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2571,7 +2464,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2579,8 +2472,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2590,16 +2481,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+          <t>kgcarcass/LU</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2609,16 +2498,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+          <t>kgcarcass/LU</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2628,16 +2515,14 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+          <t>kgcarcass/LU</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2647,19 +2532,168 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Bovines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ovines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Share of crop residues in methaniser</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Share of green waste in methaniser</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Share of dedicated culture in methaniser</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Share of animal food industry in methaniser</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Share of livestock effluent in methaniser</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
         </is>
       </c>
     </row>

--- a/src/grafs_e/data/scenario_region/Exponential/Savoie.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Savoie.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,24 +583,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Urban population</t>
+          <t>Total per capita protein ingestion</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN/cap/yr</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Logistic</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Total per capita protein ingestion</t>
+          <t>Vegetal per capita protein ingestion</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -617,7 +617,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vegetal per capita protein ingestion</t>
+          <t>Edible animal per capita protein ingestion (excl fish)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -634,24 +634,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Edible animal per capita protein ingestion (excl fish)</t>
+          <t>Arable area</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kgN/cap/yr</t>
+          <t>ha</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arable area</t>
+          <t>Permanent grassland area</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -668,24 +668,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Permanent grassland area</t>
+          <t>Import of vegetal pdcts</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ha</t>
+          <t>ktN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Import of vegetal pdcts</t>
+          <t>Export of vegetal pdcts</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -702,41 +702,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Export of vegetal pdcts</t>
+          <t>Total LU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ktN</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
+          <t>Historical trend, see prop for each livestock in technical sheet</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Total LU</t>
+          <t>Synth N fertilizer application to cropland</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>kgN/ha/yr</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Historical trend, see prop for each livestock in technical sheet</t>
+          <t>No business as usual: computed with optimization model to fertilize all crops</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Synth N fertilizer application to cropland</t>
+          <t>Synth N fertilizer application to grassland</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -753,32 +753,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Synth N fertilizer application to grassland</t>
+          <t>Methaniser production</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>kgN/ha/yr</t>
+          <t>GWh/yr</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>No business as usual: computed with optimization model to fertilize all crops</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Methaniser production</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>GWh/yr</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
         <is>
           <t>Regional 2021 data mapped on 2006 33 region plant production. Used as a goal but may be adjusted according to territory situation</t>
         </is>
@@ -1627,7 +1610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1656,6 +1639,11 @@
           <t>Comment</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1671,6 +1659,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1686,6 +1677,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1701,6 +1695,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1716,6 +1713,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1731,6 +1731,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1746,28 +1749,31 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+          <t>Urban population</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Logistic</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>%</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1779,12 +1785,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1796,12 +1805,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1813,29 +1825,35 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Historical trend</t>
-        </is>
+          <t>Taken as the last historical value</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1847,12 +1865,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1864,12 +1885,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F14" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1881,12 +1905,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F15" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1898,12 +1925,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F16" t="n">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1915,29 +1945,35 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F17" t="n">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
-        </is>
+          <t>Historical trend</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1949,12 +1985,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F19" t="n">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,12 +2005,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F20" t="n">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1983,12 +2025,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F21" t="n">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2000,12 +2045,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F22" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2017,12 +2065,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F23" t="n">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2034,12 +2085,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F24" t="n">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2051,12 +2105,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F25" t="n">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2068,12 +2125,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F26" t="n">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2085,12 +2145,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F27" t="n">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2102,12 +2165,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F28" t="n">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2119,12 +2185,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F29" t="n">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2136,12 +2205,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F30" t="n">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2153,12 +2225,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F31" t="n">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2170,12 +2245,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F32" t="n">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2187,12 +2265,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F33" t="n">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2204,12 +2285,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F34" t="n">
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2221,12 +2305,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F35" t="n">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2238,12 +2325,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F36" t="n">
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2255,12 +2345,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F37" t="n">
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2272,12 +2365,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F38" t="n">
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2289,12 +2385,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F39" t="n">
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2306,12 +2405,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F40" t="n">
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2323,29 +2425,35 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F41" t="n">
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F42" t="n">
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2357,12 +2465,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F43" t="n">
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2374,12 +2485,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F44" t="n">
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2391,12 +2505,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F45" t="n">
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2408,12 +2525,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F46" t="n">
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2425,29 +2545,35 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F47" t="n">
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
-        </is>
+          <t>Taken as the last historical value</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2459,12 +2585,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F49" t="n">
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2476,12 +2605,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F50" t="n">
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2493,12 +2625,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F51" t="n">
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2510,12 +2645,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F52" t="n">
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2527,29 +2665,35 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F53" t="n">
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F54" t="n">
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2561,12 +2705,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F55" t="n">
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2578,12 +2725,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F56" t="n">
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Poultry dairy productivity</t>
+          <t>Caprines dairy productivity</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2595,32 +2745,35 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F57" t="n">
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Share of crop residues in methaniser</t>
+          <t>Poultry dairy productivity</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>0.06</v>
+          <t>kg/LU</t>
+        </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Adapted from ONRB data</t>
-        </is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Share of green waste in methaniser</t>
+          <t>Share of crop residues in methaniser</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2629,18 +2782,21 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F59" t="n">
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Share of dedicated culture in methaniser</t>
+          <t>Share of green waste in methaniser</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2649,18 +2805,21 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F60" t="n">
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Share of animal food industry in methaniser</t>
+          <t>Share of dedicated culture in methaniser</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2669,32 +2828,61 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F61" t="n">
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>Share of animal food industry in methaniser</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>Share of livestock effluent in methaniser</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>prop</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="C63" t="n">
         <v>0.79</v>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F63" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/src/grafs_e/data/scenario_region/Exponential/Savoie.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Savoie.xlsx
@@ -778,38 +778,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Crops</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Area proportion (%)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Enforce Area</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Ymax (kgN/ha)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>k (kgN/ha)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>r2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Straw to Grain Ratio</t>
         </is>
       </c>
     </row>
@@ -834,6 +839,9 @@
       <c r="F2" t="n">
         <v>0.66</v>
       </c>
+      <c r="G2" t="n">
+        <v>0.103</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -856,6 +864,9 @@
       <c r="F3" t="n">
         <v>0.5</v>
       </c>
+      <c r="G3" t="n">
+        <v>0.114</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -878,6 +889,9 @@
       <c r="F4" t="n">
         <v>0.5600000000000001</v>
       </c>
+      <c r="G4" t="n">
+        <v>0.106</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -900,11 +914,14 @@
       <c r="F5" t="n">
         <v>0.48</v>
       </c>
+      <c r="G5" t="n">
+        <v>0.083</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Grain maize</t>
+          <t>Maize</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -922,6 +939,9 @@
       <c r="F6" t="n">
         <v>0.7</v>
       </c>
+      <c r="G6" t="n">
+        <v>0.108</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -944,6 +964,9 @@
       <c r="F7" t="n">
         <v>0</v>
       </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -966,99 +989,114 @@
       <c r="F8" t="n">
         <v>0.48</v>
       </c>
+      <c r="G8" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Straw</t>
+          <t>Rapeseed</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.8904093539845819</v>
       </c>
       <c r="C9" t="b">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>128</v>
+        <v>239</v>
       </c>
       <c r="E9" t="n">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="F9" t="n">
-        <v>0.45</v>
+        <v>0.97</v>
+      </c>
+      <c r="G9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rapeseed</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8904093539845819</v>
+        <v>0.4686365020971484</v>
       </c>
       <c r="C10" t="b">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>51</v>
       </c>
       <c r="E10" t="n">
-        <v>192</v>
+        <v>26</v>
       </c>
       <c r="F10" t="n">
-        <v>0.97</v>
+        <v>-0.09</v>
+      </c>
+      <c r="G10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Soybean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4686365020971484</v>
+        <v>1.394193593739016</v>
       </c>
       <c r="C11" t="b">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>51</v>
+        <v>411</v>
       </c>
       <c r="E11" t="n">
-        <v>26</v>
+        <v>450</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.09</v>
+        <v>0.86</v>
+      </c>
+      <c r="G11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Soybean</t>
+          <t>Other oil crops</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.394193593739016</v>
+        <v>0</v>
       </c>
       <c r="C12" t="b">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>411</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.86</v>
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Other oil crops</t>
+          <t>Horse beans and faba beans</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1068,63 +1106,72 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.97</v>
+      </c>
+      <c r="G13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Horse beans and faba beans</t>
+          <t>Peas</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.1499636806710875</v>
       </c>
       <c r="C14" t="b">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>166</v>
+        <v>323</v>
       </c>
       <c r="E14" t="n">
-        <v>211</v>
+        <v>392</v>
       </c>
       <c r="F14" t="n">
         <v>0.97</v>
       </c>
+      <c r="G14" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Peas</t>
+          <t>Other protein crops</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1499636806710875</v>
+        <v>0</v>
       </c>
       <c r="C15" t="b">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>323</v>
+        <v>215</v>
       </c>
       <c r="E15" t="n">
-        <v>392</v>
+        <v>255</v>
       </c>
       <c r="F15" t="n">
-        <v>0.97</v>
+        <v>0.74</v>
+      </c>
+      <c r="G15" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Other protein crops</t>
+          <t>Sugar beet</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1134,60 +1181,69 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>215</v>
+        <v>28</v>
       </c>
       <c r="E16" t="n">
-        <v>255</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.74</v>
+        <v>43</v>
+      </c>
+      <c r="G16" t="n">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sugar beet</t>
+          <t>Potatoes</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.5811092626004639</v>
       </c>
       <c r="C17" t="b">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>28</v>
+        <v>171</v>
       </c>
       <c r="E17" t="n">
-        <v>43</v>
+        <v>172</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G17" t="n">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Potatoes</t>
+          <t>Other roots</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5811092626004639</v>
+        <v>0</v>
       </c>
       <c r="C18" t="b">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E18" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F18" t="n">
-        <v>0.73</v>
+        <v>0.61</v>
+      </c>
+      <c r="G18" t="n">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Other roots</t>
+          <t>Green peas</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1197,19 +1253,22 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="E19" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="F19" t="n">
-        <v>0.61</v>
+        <v>0.85</v>
+      </c>
+      <c r="G19" t="n">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Green peas</t>
+          <t>Dry beans</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1219,19 +1278,22 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="E20" t="n">
-        <v>181</v>
+        <v>64</v>
       </c>
       <c r="F20" t="n">
-        <v>0.85</v>
+        <v>0.49</v>
+      </c>
+      <c r="G20" t="n">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dry beans</t>
+          <t>Green beans</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1241,19 +1303,22 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>52</v>
+        <v>262</v>
       </c>
       <c r="E21" t="n">
-        <v>64</v>
+        <v>353</v>
       </c>
       <c r="F21" t="n">
-        <v>0.49</v>
+        <v>0.91</v>
+      </c>
+      <c r="G21" t="n">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Green beans</t>
+          <t>Dry vegetables</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1263,19 +1328,22 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>262</v>
+        <v>36</v>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>0.91</v>
+        <v>-1.17</v>
+      </c>
+      <c r="G22" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dry vegetables</t>
+          <t>Dry fruits</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1285,19 +1353,22 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>36</v>
+        <v>103</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.17</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G23" t="n">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dry fruits</t>
+          <t>Squash and melons</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1307,19 +1378,22 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>103</v>
+        <v>655</v>
       </c>
       <c r="E24" t="n">
-        <v>80</v>
+        <v>519</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.99</v>
+      </c>
+      <c r="G24" t="n">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Squash and melons</t>
+          <t>Cabbage</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1329,19 +1403,22 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>655</v>
+        <v>194</v>
       </c>
       <c r="E25" t="n">
-        <v>519</v>
+        <v>159</v>
       </c>
       <c r="F25" t="n">
-        <v>0.99</v>
+        <v>0.66</v>
+      </c>
+      <c r="G25" t="n">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cabbage</t>
+          <t>Leaves vegetables</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1351,19 +1428,22 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>194</v>
+        <v>114</v>
       </c>
       <c r="E26" t="n">
-        <v>159</v>
+        <v>104</v>
       </c>
       <c r="F26" t="n">
-        <v>0.66</v>
+        <v>0.29</v>
+      </c>
+      <c r="G26" t="n">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Leaves vegetables</t>
+          <t>Fruits</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1373,19 +1453,22 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="E27" t="n">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="F27" t="n">
-        <v>0.29</v>
+        <v>0.77</v>
+      </c>
+      <c r="G27" t="n">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Fruits</t>
+          <t>Olives</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1395,19 +1478,22 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.77</v>
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Olives</t>
+          <t>Citrus</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1424,12 +1510,15 @@
       </c>
       <c r="F29" t="n">
         <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Citrus</t>
+          <t>Hemp</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1439,19 +1528,22 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>481</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Hemp</t>
+          <t>Flax</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1461,142 +1553,138 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>290</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>481</v>
+        <v>4</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>-0.13</v>
+      </c>
+      <c r="G31" t="n">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Flax</t>
+          <t>Forage maize</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>7.146706656981512</v>
       </c>
       <c r="C32" t="b">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>684</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>602</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.13</v>
+        <v>0.93</v>
+      </c>
+      <c r="G32" t="n">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Forage maize</t>
+          <t>Forage cabbages</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7.146706656981512</v>
+        <v>0</v>
       </c>
       <c r="C33" t="b">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>684</v>
+        <v>238</v>
       </c>
       <c r="E33" t="n">
-        <v>602</v>
+        <v>185</v>
       </c>
       <c r="F33" t="n">
-        <v>0.93</v>
+        <v>0.99</v>
+      </c>
+      <c r="G33" t="n">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Forage cabbages</t>
+          <t>Alfalfa and clover</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>2.425193898352743</v>
       </c>
       <c r="C34" t="b">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>238</v>
+        <v>378</v>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>487</v>
       </c>
       <c r="F34" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
+      </c>
+      <c r="G34" t="n">
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alfalfa and clover</t>
+          <t>Non-legume temporary meadow</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.425193898352743</v>
+        <v>46.65276378377112</v>
       </c>
       <c r="C35" t="b">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>378</v>
+        <v>222</v>
       </c>
       <c r="E35" t="n">
-        <v>487</v>
+        <v>227</v>
       </c>
       <c r="F35" t="n">
-        <v>0.97</v>
+        <v>0.55</v>
+      </c>
+      <c r="G35" t="n">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Non-legume temporary meadow</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>46.65276378377112</v>
+          <t xml:space="preserve">Natural meadow </t>
+        </is>
       </c>
       <c r="C36" t="b">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>222</v>
+        <v>98</v>
       </c>
       <c r="E36" t="n">
-        <v>227</v>
+        <v>88</v>
       </c>
       <c r="F36" t="n">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Natural meadow </t>
-        </is>
-      </c>
-      <c r="C37" t="b">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>98</v>
-      </c>
-      <c r="E37" t="n">
-        <v>88</v>
-      </c>
-      <c r="F37" t="n">
         <v>0.66</v>
+      </c>
+      <c r="G36" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1659,9 +1747,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1677,9 +1762,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1695,9 +1777,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1713,9 +1792,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1731,9 +1807,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1749,9 +1822,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1786,9 +1856,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1806,9 +1873,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1826,9 +1890,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1846,9 +1907,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1866,9 +1924,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1886,9 +1941,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1906,9 +1958,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1926,9 +1975,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1946,9 +1992,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v/>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1966,9 +2009,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1986,9 +2026,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2006,9 +2043,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2026,9 +2060,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2046,9 +2077,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v/>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2066,9 +2094,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2086,9 +2111,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2106,9 +2128,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v/>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2126,9 +2145,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v/>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2146,9 +2162,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v/>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2166,9 +2179,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v/>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2186,9 +2196,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v/>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2206,9 +2213,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v/>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2226,9 +2230,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2246,9 +2247,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v/>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2266,9 +2264,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v/>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2286,9 +2281,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v/>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2306,9 +2298,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v/>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2326,9 +2315,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v/>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2346,9 +2332,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v/>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2366,9 +2349,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v/>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2386,9 +2366,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v/>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2406,9 +2383,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v/>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2426,9 +2400,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v/>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2446,9 +2417,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v/>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2466,9 +2434,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v/>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2486,9 +2451,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v/>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2506,9 +2468,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v/>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2526,9 +2485,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v/>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2546,9 +2502,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v/>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2566,9 +2519,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v/>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2586,9 +2536,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v/>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2606,9 +2553,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v/>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2626,9 +2570,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v/>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2646,9 +2587,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F52" t="n">
-        <v/>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2666,9 +2604,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v/>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2686,9 +2621,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v/>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2706,9 +2638,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v/>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2726,9 +2655,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F56" t="n">
-        <v/>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2746,9 +2672,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v/>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2766,9 +2689,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v/>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2789,9 +2709,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F59" t="n">
-        <v/>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2812,9 +2729,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v/>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2835,9 +2749,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v/>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2858,9 +2769,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F62" t="n">
-        <v/>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2880,9 +2788,6 @@
         <is>
           <t>Adapted from ONRB data</t>
         </is>
-      </c>
-      <c r="F63" t="n">
-        <v/>
       </c>
     </row>
   </sheetData>
